--- a/outputs/019f416a-1d9b-7691-9c74-910f74a203d0/DNDT_Game_Components_Planning_v2.xlsx
+++ b/outputs/019f416a-1d9b-7691-9c74-910f74a203d0/DNDT_Game_Components_Planning_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Lacuna/Projects/dndt/outputs/019f416a-1d9b-7691-9c74-910f74a203d0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEA0BD8-1215-D645-9A2F-FE1B3D2ACFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F9BEB1-3AD6-B945-89A4-901CC9A8DE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1160" windowWidth="25680" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Maps &amp; Traversal" sheetId="1" r:id="rId1"/>
@@ -1210,7 +1210,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -1422,7 +1422,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -1584,20 +1584,20 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:5" s="6" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="6" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -1832,7 +1832,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -2037,7 +2037,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -2063,54 +2063,54 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" s="6" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" s="6" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" s="6" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="6" t="s">
         <v>176</v>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
